--- a/informes_data/Tercera FEB/2025-26/playoffs/individual/NP_play_by_play_2513301_ELIMINGRA12FINAL_PROCESSED.xlsx
+++ b/informes_data/Tercera FEB/2025-26/playoffs/individual/NP_play_by_play_2513301_ELIMINGRA12FINAL_PROCESSED.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>D. SAINSBURY GARCIA</t>
+          <t>S. JOKSIMOVIC</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.1786</v>
+        <v>3.2645</v>
       </c>
       <c r="E2" t="n">
-        <v>3.7821</v>
+        <v>4.2777</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.6035</v>
+        <v>-1.0132</v>
       </c>
       <c r="G2" t="n">
-        <v>0.4141</v>
+        <v>-0.6781</v>
       </c>
       <c r="H2" t="n">
-        <v>2.2245</v>
+        <v>0.1628</v>
       </c>
       <c r="I2" t="n">
-        <v>-1.8104</v>
+        <v>-0.8409</v>
       </c>
       <c r="J2" t="n">
-        <v>2.3793</v>
+        <v>2.6848</v>
       </c>
       <c r="K2" t="n">
-        <v>2.3393</v>
+        <v>1.0548</v>
       </c>
       <c r="L2" t="n">
-        <v>0.04</v>
+        <v>1.63</v>
       </c>
       <c r="M2" t="n">
-        <v>-1.9653</v>
+        <v>-3.3629</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.1149</v>
+        <v>-0.892</v>
       </c>
       <c r="O2" t="n">
-        <v>-1.8504</v>
+        <v>-2.4709</v>
       </c>
       <c r="P2" t="n">
-        <v>1.0003</v>
+        <v>0.9737</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>-1.9474</v>
       </c>
       <c r="R2" t="n">
-        <v>1.0003</v>
+        <v>2.921</v>
       </c>
       <c r="S2" t="n">
-        <v>1.3438</v>
+        <v>-0.9737</v>
       </c>
       <c r="T2" t="n">
-        <v>1.4028</v>
+        <v>-0.4024</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.059</v>
+        <v>-0.5713</v>
       </c>
       <c r="V2" t="n">
-        <v>0.4204</v>
+        <v>3.9426</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>3.9426</v>
       </c>
       <c r="X2" t="n">
-        <v>0.4204</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>S. JOKSIMOVIC</t>
+          <t>D. SAINSBURY GARCIA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.4721</v>
+        <v>2.1917</v>
       </c>
       <c r="E3" t="n">
-        <v>3.1396</v>
+        <v>2.839</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.6674</v>
+        <v>-0.6473</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.8512999999999999</v>
+        <v>0.3672</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0541</v>
+        <v>2.2332</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.9054</v>
+        <v>-1.866</v>
       </c>
       <c r="J3" t="n">
-        <v>2.2655</v>
+        <v>2.4421</v>
       </c>
       <c r="K3" t="n">
-        <v>0.8124</v>
+        <v>2.4016</v>
       </c>
       <c r="L3" t="n">
-        <v>1.4531</v>
+        <v>0.0405</v>
       </c>
       <c r="M3" t="n">
-        <v>-3.1168</v>
+        <v>-2.0749</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.7583</v>
+        <v>-0.1684</v>
       </c>
       <c r="O3" t="n">
-        <v>-2.3585</v>
+        <v>-1.9065</v>
       </c>
       <c r="P3" t="n">
-        <v>1.0003</v>
+        <v>0.9737</v>
       </c>
       <c r="Q3" t="n">
-        <v>-2.0006</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>3.0009</v>
+        <v>0.9737</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.536</v>
+        <v>0.4682</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.9845</v>
+        <v>0.3969</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.5515</v>
+        <v>0.0713</v>
       </c>
       <c r="V3" t="n">
-        <v>3.8591</v>
+        <v>0.3826</v>
       </c>
       <c r="W3" t="n">
-        <v>3.8591</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>0.3826</v>
       </c>
     </row>
     <row r="4">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.739</v>
+        <v>1.7389</v>
       </c>
       <c r="E4" t="n">
-        <v>0.2687</v>
+        <v>0.2977</v>
       </c>
       <c r="F4" t="n">
-        <v>1.4703</v>
+        <v>1.4412</v>
       </c>
       <c r="G4" t="n">
-        <v>1.4829</v>
+        <v>1.4372</v>
       </c>
       <c r="H4" t="n">
-        <v>0.2937</v>
+        <v>0.2637</v>
       </c>
       <c r="I4" t="n">
-        <v>1.1892</v>
+        <v>1.1735</v>
       </c>
       <c r="J4" t="n">
-        <v>0.7199</v>
+        <v>0.7305</v>
       </c>
       <c r="K4" t="n">
-        <v>0.08</v>
+        <v>0.08210000000000001</v>
       </c>
       <c r="L4" t="n">
-        <v>0.6399</v>
+        <v>0.6484</v>
       </c>
       <c r="M4" t="n">
-        <v>0.763</v>
+        <v>0.7067</v>
       </c>
       <c r="N4" t="n">
-        <v>0.2138</v>
+        <v>0.1816</v>
       </c>
       <c r="O4" t="n">
-        <v>0.5493</v>
+        <v>0.525</v>
       </c>
       <c r="P4" t="n">
-        <v>1.2003</v>
+        <v>1.1684</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.2003</v>
+        <v>1.1684</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.6844</v>
+        <v>-0.5872000000000001</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.4512</v>
+        <v>-0.4328</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.2332</v>
+        <v>-0.1544</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.2598</v>
+        <v>-0.2795</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.2598</v>
+        <v>-0.2795</v>
       </c>
     </row>
     <row r="5">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.392</v>
+        <v>0.6982</v>
       </c>
       <c r="E5" t="n">
-        <v>2.343</v>
+        <v>3.1482</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.951</v>
+        <v>-2.4501</v>
       </c>
       <c r="G5" t="n">
-        <v>0.2246</v>
+        <v>0.2206</v>
       </c>
       <c r="H5" t="n">
-        <v>2.5862</v>
+        <v>2.6361</v>
       </c>
       <c r="I5" t="n">
-        <v>-2.3616</v>
+        <v>-2.4155</v>
       </c>
       <c r="J5" t="n">
-        <v>2.8702</v>
+        <v>3.1177</v>
       </c>
       <c r="K5" t="n">
-        <v>3.5444</v>
+        <v>3.7333</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.6742</v>
+        <v>-0.6156</v>
       </c>
       <c r="M5" t="n">
-        <v>-2.6456</v>
+        <v>-2.8971</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.9582000000000001</v>
+        <v>-1.0973</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.6874</v>
+        <v>-1.7999</v>
       </c>
       <c r="P5" t="n">
-        <v>1.6005</v>
+        <v>1.5579</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.0003</v>
+        <v>-0.9737</v>
       </c>
       <c r="R5" t="n">
-        <v>2.6007</v>
+        <v>2.5316</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.8332000000000001</v>
+        <v>-0.4698</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.7267</v>
+        <v>-0.2169</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.1065</v>
+        <v>-0.2529</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.5999</v>
+        <v>-0.6105</v>
       </c>
       <c r="W5" t="n">
-        <v>1.1998</v>
+        <v>1.2211</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.7997</v>
+        <v>-1.8316</v>
       </c>
     </row>
     <row r="6">
@@ -877,64 +877,64 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.388</v>
+        <v>0.2896</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.9881</v>
+        <v>-0.9729</v>
       </c>
       <c r="F6" t="n">
-        <v>1.376</v>
+        <v>1.2625</v>
       </c>
       <c r="G6" t="n">
-        <v>1.5096</v>
+        <v>1.4638</v>
       </c>
       <c r="H6" t="n">
-        <v>1.1379</v>
+        <v>1.1366</v>
       </c>
       <c r="I6" t="n">
-        <v>0.3718</v>
+        <v>0.3272</v>
       </c>
       <c r="J6" t="n">
-        <v>1.4614</v>
+        <v>1.5308</v>
       </c>
       <c r="K6" t="n">
-        <v>1.3814</v>
+        <v>1.4497</v>
       </c>
       <c r="L6" t="n">
-        <v>0.08</v>
+        <v>0.08110000000000001</v>
       </c>
       <c r="M6" t="n">
-        <v>0.0482</v>
+        <v>-0.067</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.2435</v>
+        <v>-0.3131</v>
       </c>
       <c r="O6" t="n">
-        <v>0.2918</v>
+        <v>0.2461</v>
       </c>
       <c r="P6" t="n">
-        <v>0.6002</v>
+        <v>0.5842000000000001</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.0003</v>
+        <v>-0.9737</v>
       </c>
       <c r="R6" t="n">
-        <v>1.6005</v>
+        <v>1.5579</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.3614</v>
+        <v>-0.4342</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.0888</v>
+        <v>-0.2058</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.2726</v>
+        <v>-0.2284</v>
       </c>
       <c r="V6" t="n">
-        <v>-1.3604</v>
+        <v>-1.3242</v>
       </c>
       <c r="W6" t="n">
-        <v>-1.3604</v>
+        <v>-1.3242</v>
       </c>
       <c r="X6" t="n">
         <v>0</v>
@@ -955,64 +955,64 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.62</v>
+        <v>-0.2144</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.9008</v>
+        <v>-1.5045</v>
       </c>
       <c r="F7" t="n">
-        <v>1.2807</v>
+        <v>1.2901</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.4</v>
+        <v>-1.4021</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.3368</v>
+        <v>-1.2525</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.06320000000000001</v>
+        <v>-0.1496</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.9471000000000001</v>
+        <v>-0.7536</v>
       </c>
       <c r="K7" t="n">
-        <v>-1.107</v>
+        <v>-0.9157</v>
       </c>
       <c r="L7" t="n">
-        <v>0.16</v>
+        <v>0.1621</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.4529</v>
+        <v>-0.6485</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.2297</v>
+        <v>-0.3367</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.2232</v>
+        <v>-0.3117</v>
       </c>
       <c r="P7" t="n">
-        <v>2.6007</v>
+        <v>2.5316</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>2.6007</v>
+        <v>2.5316</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.4004</v>
+        <v>-0.9612000000000001</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.5333</v>
+        <v>-0.3682</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.8671</v>
+        <v>-0.593</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.4204</v>
+        <v>-0.3826</v>
       </c>
       <c r="W7" t="n">
-        <v>-0.4204</v>
+        <v>-0.3826</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
@@ -1033,40 +1033,40 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.1538</v>
+        <v>-1.1449</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.1089</v>
+        <v>-0.1031</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.0448</v>
+        <v>-1.0418</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.9086</v>
+        <v>-0.9347</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.3799</v>
+        <v>-0.39</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.5286999999999999</v>
+        <v>-0.5447</v>
       </c>
       <c r="J8" t="n">
-        <v>0.02</v>
+        <v>0.0205</v>
       </c>
       <c r="K8" t="n">
-        <v>0.02</v>
+        <v>0.0205</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.9286</v>
+        <v>-0.9553</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.3999</v>
+        <v>-0.4105</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.5286999999999999</v>
+        <v>-0.5447</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
@@ -1078,13 +1078,13 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.2452</v>
+        <v>-0.2102</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.1289</v>
+        <v>-0.1237</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.1163</v>
+        <v>-0.08649999999999999</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.8335</v>
+        <v>-1.4318</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.5394</v>
+        <v>-0.1489</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.2941</v>
+        <v>-1.2829</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.5925</v>
+        <v>-0.6483</v>
       </c>
       <c r="H9" t="n">
-        <v>1.2735</v>
+        <v>1.2695</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.866</v>
+        <v>-1.9179</v>
       </c>
       <c r="J9" t="n">
-        <v>0.8234</v>
+        <v>0.9068000000000001</v>
       </c>
       <c r="K9" t="n">
-        <v>1.3814</v>
+        <v>1.4497</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.5580000000000001</v>
+        <v>-0.5429</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.4159</v>
+        <v>-1.5551</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.1079</v>
+        <v>-0.1802</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.308</v>
+        <v>-1.3749</v>
       </c>
       <c r="P9" t="n">
-        <v>0.8002</v>
+        <v>0.7789</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.0003</v>
+        <v>-0.9737</v>
       </c>
       <c r="R9" t="n">
-        <v>1.8005</v>
+        <v>1.7526</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.7611</v>
+        <v>-0.2898</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.2822</v>
+        <v>-0.0304</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.4789</v>
+        <v>-0.2594</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.2801</v>
+        <v>-1.2726</v>
       </c>
       <c r="W9" t="n">
-        <v>-0.0803</v>
+        <v>-0.0516</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.1998</v>
+        <v>-1.2211</v>
       </c>
     </row>
     <row r="10">
@@ -1189,58 +1189,58 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.8466</v>
+        <v>-5.0675</v>
       </c>
       <c r="E10" t="n">
-        <v>-6.1073</v>
+        <v>-5.2302</v>
       </c>
       <c r="F10" t="n">
-        <v>1.2607</v>
+        <v>0.1627</v>
       </c>
       <c r="G10" t="n">
-        <v>-2.4891</v>
+        <v>-2.4766</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.2455</v>
+        <v>-1.1714</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.2436</v>
+        <v>-1.3052</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.0435</v>
+        <v>0.2205</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.0873</v>
+        <v>0.1311</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0438</v>
+        <v>0.08939999999999999</v>
       </c>
       <c r="M10" t="n">
-        <v>-2.4456</v>
+        <v>-2.6971</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.1582</v>
+        <v>-1.3025</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.2874</v>
+        <v>-1.3946</v>
       </c>
       <c r="P10" t="n">
-        <v>-1.8005</v>
+        <v>-1.7526</v>
       </c>
       <c r="Q10" t="n">
-        <v>-5.0014</v>
+        <v>-4.8684</v>
       </c>
       <c r="R10" t="n">
-        <v>3.2009</v>
+        <v>3.1158</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.5570000000000001</v>
+        <v>-0.8383</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.0623</v>
+        <v>-0.5823</v>
       </c>
       <c r="U10" t="n">
-        <v>0.5054</v>
+        <v>-0.2559</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.2841999999999985</v>
+        <v>0.3243</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.1111000000000004</v>
+        <v>2.603</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.1731000000000003</v>
+        <v>-2.2788</v>
       </c>
       <c r="G11" t="n">
-        <v>-2.6103</v>
+        <v>-2.651</v>
       </c>
       <c r="H11" t="n">
-        <v>4.6077</v>
+        <v>4.888</v>
       </c>
       <c r="I11" t="n">
-        <v>-7.217899999999999</v>
+        <v>-7.5391</v>
       </c>
       <c r="J11" t="n">
-        <v>9.549099999999999</v>
+        <v>10.9001</v>
       </c>
       <c r="K11" t="n">
-        <v>8.364599999999999</v>
+        <v>9.4071</v>
       </c>
       <c r="L11" t="n">
-        <v>1.1846</v>
+        <v>1.493</v>
       </c>
       <c r="M11" t="n">
-        <v>-12.1595</v>
+        <v>-13.5512</v>
       </c>
       <c r="N11" t="n">
-        <v>-3.7568</v>
+        <v>-4.5191</v>
       </c>
       <c r="O11" t="n">
-        <v>-8.4025</v>
+        <v>-9.0321</v>
       </c>
       <c r="P11" t="n">
-        <v>7.001999999999999</v>
+        <v>6.8158</v>
       </c>
       <c r="Q11" t="n">
-        <v>-10.0029</v>
+        <v>-9.7369</v>
       </c>
       <c r="R11" t="n">
-        <v>17.0048</v>
+        <v>16.5526</v>
       </c>
       <c r="S11" t="n">
-        <v>-5.0349</v>
+        <v>-4.2962</v>
       </c>
       <c r="T11" t="n">
-        <v>-2.8551</v>
+        <v>-1.9656</v>
       </c>
       <c r="U11" t="n">
-        <v>-2.1797</v>
+        <v>-2.3305</v>
       </c>
       <c r="V11" t="n">
-        <v>0.3589000000000002</v>
+        <v>0.4557999999999995</v>
       </c>
       <c r="W11" t="n">
-        <v>3.1978</v>
+        <v>3.4053</v>
       </c>
       <c r="X11" t="n">
-        <v>-2.8389</v>
+        <v>-2.9496</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>I. ARTECHE URRUZOLA</t>
+          <t>J. EGAA AYERZA</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,73 +1345,73 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>8.3436</v>
+        <v>6.9053</v>
       </c>
       <c r="E12" t="n">
-        <v>5.8636</v>
+        <v>6.2794</v>
       </c>
       <c r="F12" t="n">
-        <v>2.48</v>
+        <v>0.6259</v>
       </c>
       <c r="G12" t="n">
-        <v>1.4942</v>
+        <v>3.5616</v>
       </c>
       <c r="H12" t="n">
-        <v>0.0982</v>
+        <v>-0.407</v>
       </c>
       <c r="I12" t="n">
-        <v>1.396</v>
+        <v>3.9686</v>
       </c>
       <c r="J12" t="n">
-        <v>2.6249</v>
+        <v>4.9273</v>
       </c>
       <c r="K12" t="n">
-        <v>0.9851</v>
+        <v>0.5337</v>
       </c>
       <c r="L12" t="n">
-        <v>1.6398</v>
+        <v>4.3936</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.1307</v>
+        <v>-1.3657</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.887</v>
+        <v>-0.9407</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.2438</v>
+        <v>-0.4249</v>
       </c>
       <c r="P12" t="n">
-        <v>1.6005</v>
+        <v>0.9737</v>
       </c>
       <c r="Q12" t="n">
-        <v>-0.2001</v>
+        <v>-0.1947</v>
       </c>
       <c r="R12" t="n">
-        <v>1.8005</v>
+        <v>1.1684</v>
       </c>
       <c r="S12" t="n">
-        <v>4.5688</v>
+        <v>0.4868</v>
       </c>
       <c r="T12" t="n">
-        <v>3.179</v>
+        <v>0.3258</v>
       </c>
       <c r="U12" t="n">
-        <v>1.3899</v>
+        <v>0.161</v>
       </c>
       <c r="V12" t="n">
-        <v>0.6802</v>
+        <v>1.8832</v>
       </c>
       <c r="W12" t="n">
-        <v>0.2598</v>
+        <v>1.2211</v>
       </c>
       <c r="X12" t="n">
-        <v>0.4204</v>
+        <v>0.6621</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>J. EGAA AYERZA</t>
+          <t>I. ARTECHE URRUZOLA</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1423,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>5.5083</v>
+        <v>5.6966</v>
       </c>
       <c r="E13" t="n">
-        <v>5.0642</v>
+        <v>4.0983</v>
       </c>
       <c r="F13" t="n">
-        <v>0.4441</v>
+        <v>1.5983</v>
       </c>
       <c r="G13" t="n">
-        <v>3.551</v>
+        <v>1.4388</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.3166</v>
+        <v>0.0692</v>
       </c>
       <c r="I13" t="n">
-        <v>3.8676</v>
+        <v>1.3695</v>
       </c>
       <c r="J13" t="n">
-        <v>4.7669</v>
+        <v>2.7675</v>
       </c>
       <c r="K13" t="n">
-        <v>0.5199</v>
+        <v>1.106</v>
       </c>
       <c r="L13" t="n">
-        <v>4.247</v>
+        <v>1.6616</v>
       </c>
       <c r="M13" t="n">
-        <v>-1.2158</v>
+        <v>-1.3288</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.8365</v>
+        <v>-1.0367</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.3794</v>
+        <v>-0.292</v>
       </c>
       <c r="P13" t="n">
-        <v>1.0003</v>
+        <v>1.5579</v>
       </c>
       <c r="Q13" t="n">
-        <v>-0.2001</v>
+        <v>-0.1947</v>
       </c>
       <c r="R13" t="n">
-        <v>1.2003</v>
+        <v>1.7526</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.9229000000000001</v>
+        <v>2.0378</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.7023</v>
+        <v>1.246</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.2206</v>
+        <v>0.7917999999999999</v>
       </c>
       <c r="V13" t="n">
-        <v>1.88</v>
+        <v>0.6621</v>
       </c>
       <c r="W13" t="n">
-        <v>1.1998</v>
+        <v>0.2795</v>
       </c>
       <c r="X13" t="n">
-        <v>0.6802</v>
+        <v>0.3826</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A. ZABALETA LASA</t>
+          <t>I. SAGASTI ARGOTE</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.0474</v>
+        <v>1.3611</v>
       </c>
       <c r="E14" t="n">
-        <v>3.7038</v>
+        <v>1.0032</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.6563</v>
+        <v>0.3579</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.1676</v>
+        <v>0.9006</v>
       </c>
       <c r="H14" t="n">
-        <v>1.1328</v>
+        <v>0.7271</v>
       </c>
       <c r="I14" t="n">
-        <v>-1.3004</v>
+        <v>0.1734</v>
       </c>
       <c r="J14" t="n">
-        <v>2.5904</v>
+        <v>0.9847</v>
       </c>
       <c r="K14" t="n">
-        <v>2.7047</v>
+        <v>0.9442</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.1143</v>
+        <v>0.0405</v>
       </c>
       <c r="M14" t="n">
-        <v>-2.758</v>
+        <v>-0.0842</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.5719</v>
+        <v>-0.2171</v>
       </c>
       <c r="O14" t="n">
-        <v>-1.1861</v>
+        <v>0.1329</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.4001</v>
+        <v>0.1947</v>
       </c>
       <c r="Q14" t="n">
-        <v>-2.2006</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1.8005</v>
+        <v>0.1947</v>
       </c>
       <c r="S14" t="n">
-        <v>3.8149</v>
+        <v>0.2658</v>
       </c>
       <c r="T14" t="n">
-        <v>2.1142</v>
+        <v>0.0185</v>
       </c>
       <c r="U14" t="n">
-        <v>1.7007</v>
+        <v>0.2473</v>
       </c>
       <c r="V14" t="n">
-        <v>-1.1998</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>1.1998</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>-2.3995</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>I. SAGASTI ARGOTE</t>
+          <t>M. LARRANAGA ORMAZABAL</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.6643</v>
+        <v>0.9836</v>
       </c>
       <c r="E15" t="n">
-        <v>1.3799</v>
+        <v>0.0363</v>
       </c>
       <c r="F15" t="n">
-        <v>0.2844</v>
+        <v>0.9473</v>
       </c>
       <c r="G15" t="n">
-        <v>0.9023</v>
+        <v>1.5958</v>
       </c>
       <c r="H15" t="n">
-        <v>0.7267</v>
+        <v>0.0898</v>
       </c>
       <c r="I15" t="n">
-        <v>0.1756</v>
+        <v>1.506</v>
       </c>
       <c r="J15" t="n">
-        <v>0.9597</v>
+        <v>1.2813</v>
       </c>
       <c r="K15" t="n">
-        <v>0.9197</v>
+        <v>0.0411</v>
       </c>
       <c r="L15" t="n">
-        <v>0.04</v>
+        <v>1.2402</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.0574</v>
+        <v>0.3145</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.193</v>
+        <v>0.0487</v>
       </c>
       <c r="O15" t="n">
-        <v>0.1356</v>
+        <v>0.2658</v>
       </c>
       <c r="P15" t="n">
-        <v>0.2001</v>
+        <v>-0.5842000000000001</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>-0.9737</v>
       </c>
       <c r="R15" t="n">
-        <v>0.2001</v>
+        <v>0.3895</v>
       </c>
       <c r="S15" t="n">
-        <v>0.5620000000000001</v>
+        <v>-0.0796</v>
       </c>
       <c r="T15" t="n">
-        <v>0.4202</v>
+        <v>-0.2713</v>
       </c>
       <c r="U15" t="n">
-        <v>0.1418</v>
+        <v>0.1917</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>0.0516</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>0.0516</v>
       </c>
     </row>
     <row r="16">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.0114</v>
+        <v>0.9012</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.2112</v>
+        <v>0.0102</v>
       </c>
       <c r="F16" t="n">
-        <v>1.2226</v>
+        <v>0.891</v>
       </c>
       <c r="G16" t="n">
-        <v>0.5319</v>
+        <v>0.474</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.3461</v>
+        <v>-0.3931</v>
       </c>
       <c r="I16" t="n">
-        <v>0.878</v>
+        <v>0.8671</v>
       </c>
       <c r="J16" t="n">
-        <v>0.24</v>
+        <v>0.2437</v>
       </c>
       <c r="K16" t="n">
-        <v>0.04</v>
+        <v>0.0411</v>
       </c>
       <c r="L16" t="n">
-        <v>0.2</v>
+        <v>0.2026</v>
       </c>
       <c r="M16" t="n">
-        <v>0.2919</v>
+        <v>0.2303</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.3861</v>
+        <v>-0.4342</v>
       </c>
       <c r="O16" t="n">
-        <v>0.678</v>
+        <v>0.6645</v>
       </c>
       <c r="P16" t="n">
-        <v>0.2001</v>
+        <v>0.1947</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>0.2001</v>
+        <v>0.1947</v>
       </c>
       <c r="S16" t="n">
-        <v>0.1991</v>
+        <v>0.1809</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.4512</v>
+        <v>-0.2335</v>
       </c>
       <c r="U16" t="n">
-        <v>0.6503</v>
+        <v>0.4144</v>
       </c>
       <c r="V16" t="n">
-        <v>0.0803</v>
+        <v>0.0516</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>0.0803</v>
+        <v>0.0516</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>M. LARRANAGA ORMAZABAL</t>
+          <t>A. ZABALETA LASA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.7806999999999999</v>
+        <v>0.3873</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.1453</v>
+        <v>2.9098</v>
       </c>
       <c r="F17" t="n">
-        <v>0.926</v>
+        <v>-2.5225</v>
       </c>
       <c r="G17" t="n">
-        <v>1.5911</v>
+        <v>-0.0953</v>
       </c>
       <c r="H17" t="n">
-        <v>0.1182</v>
+        <v>1.1818</v>
       </c>
       <c r="I17" t="n">
-        <v>1.4729</v>
+        <v>-1.2772</v>
       </c>
       <c r="J17" t="n">
-        <v>1.2417</v>
+        <v>2.823</v>
       </c>
       <c r="K17" t="n">
-        <v>0.04</v>
+        <v>2.8712</v>
       </c>
       <c r="L17" t="n">
-        <v>1.2017</v>
+        <v>-0.0483</v>
       </c>
       <c r="M17" t="n">
-        <v>0.3494</v>
+        <v>-2.9183</v>
       </c>
       <c r="N17" t="n">
-        <v>0.07820000000000001</v>
+        <v>-1.6894</v>
       </c>
       <c r="O17" t="n">
-        <v>0.2712</v>
+        <v>-1.2289</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.6002</v>
+        <v>-0.3895</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.0003</v>
+        <v>-2.1421</v>
       </c>
       <c r="R17" t="n">
-        <v>0.4001</v>
+        <v>1.7526</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.2905</v>
+        <v>2.0932</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.3867</v>
+        <v>1.0079</v>
       </c>
       <c r="U17" t="n">
-        <v>0.09619999999999999</v>
+        <v>1.0853</v>
       </c>
       <c r="V17" t="n">
-        <v>0.0803</v>
+        <v>-1.2211</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.2211</v>
       </c>
       <c r="X17" t="n">
-        <v>0.0803</v>
+        <v>-2.4421</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. EGUSKITZA AGINALDE</t>
+          <t>A. BOZAL GOMEZ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-2.7911</v>
+        <v>-1.805</v>
       </c>
       <c r="E18" t="n">
-        <v>-2.1411</v>
+        <v>-0.5264</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.6501</v>
+        <v>-1.2786</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.3397</v>
+        <v>-0.5916</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.6421</v>
+        <v>0.5187</v>
       </c>
       <c r="I18" t="n">
-        <v>0.3024</v>
+        <v>-1.1103</v>
       </c>
       <c r="J18" t="n">
-        <v>-1.1742</v>
+        <v>0.7675</v>
       </c>
       <c r="K18" t="n">
-        <v>-1.3342</v>
+        <v>1.3266</v>
       </c>
       <c r="L18" t="n">
-        <v>0.16</v>
+        <v>-0.5590000000000001</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.1654</v>
+        <v>-1.3591</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.3079</v>
+        <v>-0.8078</v>
       </c>
       <c r="O18" t="n">
-        <v>0.1425</v>
+        <v>-0.5513</v>
       </c>
       <c r="P18" t="n">
-        <v>-2.0006</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>-2.0006</v>
+        <v>-0.9737</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>0.9737</v>
       </c>
       <c r="S18" t="n">
-        <v>0.5491</v>
+        <v>0.0076</v>
       </c>
       <c r="T18" t="n">
-        <v>1.0337</v>
+        <v>-0.3202</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.4846</v>
+        <v>0.3279</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>-1.2211</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-1.2211</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. BOZAL GOMEZ</t>
+          <t>E. ANDRES CAMPOS</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-3.015</v>
+        <v>-2.383</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.2951</v>
+        <v>-1.6357</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.7199</v>
+        <v>-0.7473</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.5573</v>
+        <v>-1.0542</v>
       </c>
       <c r="H19" t="n">
-        <v>0.5606</v>
+        <v>-0.1597</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.1179</v>
+        <v>-0.8945</v>
       </c>
       <c r="J19" t="n">
-        <v>0.6653</v>
+        <v>0.7338</v>
       </c>
       <c r="K19" t="n">
-        <v>1.2614</v>
+        <v>1.2034</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.5961</v>
+        <v>-0.4696</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.2227</v>
+        <v>-1.788</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.7009</v>
+        <v>-1.3631</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.5218</v>
+        <v>-0.4249</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>-0.7789</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.0003</v>
+        <v>-2.1421</v>
       </c>
       <c r="R19" t="n">
-        <v>1.0003</v>
+        <v>1.3632</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.2579</v>
+        <v>0.3918</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.9602000000000001</v>
+        <v>0.4347</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.2977</v>
+        <v>-0.0429</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.1998</v>
+        <v>-0.9416</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>-0.6621</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.1998</v>
+        <v>-0.2795</v>
       </c>
     </row>
     <row r="20">
@@ -1969,58 +1969,58 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.8422</v>
+        <v>-3.2489</v>
       </c>
       <c r="E20" t="n">
-        <v>-4.553</v>
+        <v>-4.0815</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7108</v>
+        <v>0.8326</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.8865</v>
+        <v>-0.9082</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.2171</v>
+        <v>-1.2747</v>
       </c>
       <c r="I20" t="n">
-        <v>0.3306</v>
+        <v>0.3665</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.7141999999999999</v>
+        <v>-0.6556</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.638</v>
+        <v>-0.6235000000000001</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.0762</v>
+        <v>-0.0322</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.1723</v>
+        <v>-0.2526</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.5790999999999999</v>
+        <v>-0.6513</v>
       </c>
       <c r="O20" t="n">
-        <v>0.4068</v>
+        <v>0.3987</v>
       </c>
       <c r="P20" t="n">
-        <v>-2.4007</v>
+        <v>-2.3368</v>
       </c>
       <c r="Q20" t="n">
-        <v>-3.0009</v>
+        <v>-2.921</v>
       </c>
       <c r="R20" t="n">
-        <v>0.6002</v>
+        <v>0.5842000000000001</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.5551</v>
+        <v>-0.0039</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.8379</v>
+        <v>-0.5048</v>
       </c>
       <c r="U20" t="n">
-        <v>0.2829</v>
+        <v>0.5009</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>E. ANDRES CAMPOS</t>
+          <t>A. EGUSKITZA AGINALDE</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.8828</v>
+        <v>-3.2978</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.9873</v>
+        <v>-2.8379</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.8955</v>
+        <v>-0.4599</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.0196</v>
+        <v>-1.3721</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.08799999999999999</v>
+        <v>-1.6606</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.9317</v>
+        <v>0.2884</v>
       </c>
       <c r="J21" t="n">
-        <v>0.5891999999999999</v>
+        <v>-1.113</v>
       </c>
       <c r="K21" t="n">
-        <v>1.1415</v>
+        <v>-1.2751</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.5523</v>
+        <v>0.1621</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.6088</v>
+        <v>-0.2591</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.2294</v>
+        <v>-0.3855</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.3794</v>
+        <v>0.1263</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.8002</v>
+        <v>-1.9474</v>
       </c>
       <c r="Q21" t="n">
-        <v>-2.2006</v>
+        <v>-1.9474</v>
       </c>
       <c r="R21" t="n">
-        <v>1.4004</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.123</v>
+        <v>0.0217</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.6957</v>
+        <v>0.2224</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.4273</v>
+        <v>-0.2007</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.9399999999999999</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>-0.6802</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.2598</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-5.5404</v>
+        <v>-3.8772</v>
       </c>
       <c r="E22" t="n">
-        <v>-4.5053</v>
+        <v>-2.9769</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.0351</v>
+        <v>-0.9004</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.4895</v>
+        <v>-1.2982</v>
       </c>
       <c r="H22" t="n">
-        <v>-3.6343</v>
+        <v>-3.5796</v>
       </c>
       <c r="I22" t="n">
-        <v>2.1448</v>
+        <v>2.2814</v>
       </c>
       <c r="J22" t="n">
-        <v>0.3698</v>
+        <v>0.7911</v>
       </c>
       <c r="K22" t="n">
-        <v>-1.8832</v>
+        <v>-1.6495</v>
       </c>
       <c r="L22" t="n">
-        <v>2.253</v>
+        <v>2.4406</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.8593</v>
+        <v>-2.0893</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.7511</v>
+        <v>-1.9301</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.1082</v>
+        <v>-0.1591</v>
       </c>
       <c r="P22" t="n">
-        <v>-3.8011</v>
+        <v>-3.7</v>
       </c>
       <c r="Q22" t="n">
-        <v>-5.2015</v>
+        <v>-5.0631</v>
       </c>
       <c r="R22" t="n">
-        <v>1.4004</v>
+        <v>1.3632</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.5097</v>
+        <v>0.8415</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.5333</v>
+        <v>0.4052</v>
       </c>
       <c r="U22" t="n">
-        <v>0.0236</v>
+        <v>0.4363</v>
       </c>
       <c r="V22" t="n">
-        <v>0.2598</v>
+        <v>0.2795</v>
       </c>
       <c r="W22" t="n">
-        <v>0.8597</v>
+        <v>0.89</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.5999</v>
+        <v>-0.6105</v>
       </c>
     </row>
     <row r="23">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>0.2842000000000002</v>
+        <v>1.623200000000001</v>
       </c>
       <c r="E23" t="n">
-        <v>0.1731999999999978</v>
+        <v>2.278800000000003</v>
       </c>
       <c r="F23" t="n">
-        <v>0.111</v>
+        <v>-0.6556999999999996</v>
       </c>
       <c r="G23" t="n">
-        <v>2.6103</v>
+        <v>2.6512</v>
       </c>
       <c r="H23" t="n">
-        <v>-4.607699999999999</v>
+        <v>-4.888100000000001</v>
       </c>
       <c r="I23" t="n">
-        <v>7.217899999999999</v>
+        <v>7.538900000000002</v>
       </c>
       <c r="J23" t="n">
-        <v>12.1595</v>
+        <v>13.5513</v>
       </c>
       <c r="K23" t="n">
-        <v>3.756899999999999</v>
+        <v>4.5192</v>
       </c>
       <c r="L23" t="n">
-        <v>8.4026</v>
+        <v>9.0321</v>
       </c>
       <c r="M23" t="n">
-        <v>-9.549099999999999</v>
+        <v>-10.9003</v>
       </c>
       <c r="N23" t="n">
-        <v>-8.364699999999999</v>
+        <v>-9.407200000000001</v>
       </c>
       <c r="O23" t="n">
-        <v>-1.1846</v>
+        <v>-1.4929</v>
       </c>
       <c r="P23" t="n">
-        <v>-7.0019</v>
+        <v>-6.8158</v>
       </c>
       <c r="Q23" t="n">
-        <v>-17.005</v>
+        <v>-16.5525</v>
       </c>
       <c r="R23" t="n">
-        <v>10.0029</v>
+        <v>9.736799999999999</v>
       </c>
       <c r="S23" t="n">
-        <v>5.034799999999999</v>
+        <v>6.2436</v>
       </c>
       <c r="T23" t="n">
-        <v>2.179799999999999</v>
+        <v>2.3307</v>
       </c>
       <c r="U23" t="n">
-        <v>2.8552</v>
+        <v>3.913</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.3589999999999998</v>
+        <v>-0.4558</v>
       </c>
       <c r="W23" t="n">
-        <v>2.8389</v>
+        <v>2.9496</v>
       </c>
       <c r="X23" t="n">
-        <v>-3.1978</v>
+        <v>-3.4053</v>
       </c>
     </row>
   </sheetData>
